--- a/Entregables/diagrama de gantt-diseño_e_implementacion.xlsx
+++ b/Entregables/diagrama de gantt-diseño_e_implementacion.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Emanuel\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\M\Biblioteca-Tec\Entregables\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -14,7 +14,7 @@
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="152511"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -24,60 +24,57 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t xml:space="preserve">Actividad </t>
   </si>
   <si>
-    <t>mayo</t>
-  </si>
-  <si>
-    <t>junio</t>
-  </si>
-  <si>
-    <t>julio</t>
-  </si>
-  <si>
-    <t>agosto</t>
-  </si>
-  <si>
-    <t>septiembre</t>
-  </si>
-  <si>
-    <t>octubre</t>
-  </si>
-  <si>
-    <t>noviembre</t>
-  </si>
-  <si>
     <t>Fase de analisis</t>
   </si>
   <si>
-    <t>diseño de datos</t>
-  </si>
-  <si>
-    <t>desarrollo backend</t>
-  </si>
-  <si>
-    <t>desarrollo de frontend</t>
-  </si>
-  <si>
-    <t>agregar README</t>
-  </si>
-  <si>
-    <t>////////////</t>
-  </si>
-  <si>
-    <t>pruebas</t>
-  </si>
-  <si>
-    <t>documentacion</t>
+    <t>Mayo</t>
+  </si>
+  <si>
+    <t>Junio</t>
+  </si>
+  <si>
+    <t>Julio</t>
+  </si>
+  <si>
+    <t>Agosto</t>
+  </si>
+  <si>
+    <t>Septiembre</t>
+  </si>
+  <si>
+    <t>Octubre</t>
+  </si>
+  <si>
+    <t>Noviembre</t>
+  </si>
+  <si>
+    <t>Diseño de datos</t>
+  </si>
+  <si>
+    <t>Desarrollo backend</t>
+  </si>
+  <si>
+    <t>Desarrollo de frontend</t>
+  </si>
+  <si>
+    <t>Pruebas</t>
+  </si>
+  <si>
+    <t>Agregar README</t>
+  </si>
+  <si>
+    <t>Documentacion</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -87,7 +84,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="17">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -102,12 +99,90 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0"/>
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="-0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="-0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC00000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF8601"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF69BE02"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF91A917"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -115,20 +190,69 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FF69BE02"/>
+      <color rgb="FF91A917"/>
+      <color rgb="FFFF8601"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -403,94 +527,149 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="C1" t="s">
+      <c r="B1" s="10"/>
+      <c r="C1" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="10"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="D1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="1" t="s">
+      <c r="B2" s="10"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="10"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="10"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="10"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="10"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="10"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="10"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="16"/>
+      <c r="H5" s="5"/>
+      <c r="I5" s="5"/>
+      <c r="J5" s="10"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="10"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="6"/>
+      <c r="H6" s="15"/>
+      <c r="I6" s="6"/>
+      <c r="J6" s="10"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5" s="1"/>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="B7" s="10"/>
+      <c r="C7" s="7"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="15"/>
+      <c r="I7" s="12"/>
+      <c r="J7" s="10"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="1"/>
-      <c r="H6" s="1"/>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>12</v>
-      </c>
-      <c r="I7" s="1"/>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>15</v>
-      </c>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
+      <c r="B8" s="10"/>
+      <c r="C8" s="9"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="14"/>
       <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
+      <c r="G8" s="16"/>
+      <c r="H8" s="15"/>
+      <c r="I8" s="12"/>
+      <c r="J8" s="10"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="10"/>
+      <c r="B9" s="10"/>
+      <c r="C9" s="10"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="10"/>
+      <c r="F9" s="10"/>
+      <c r="G9" s="10"/>
+      <c r="H9" s="10"/>
+      <c r="I9" s="10"/>
+      <c r="J9" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
